--- a/product_upload/packages/41/file.xlsx
+++ b/product_upload/packages/41/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>CORREX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-38534743A1A4</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1014,6 +1024,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>CAVERTA 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-F4C3861D7E45</t>
         </is>
       </c>
@@ -1037,7 +1052,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1196,6 +1211,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>DIAPHAGE 1 G SR TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-34901A706D5A</t>
         </is>
       </c>
@@ -1219,7 +1239,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1378,6 +1398,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Ravildo 3.125 mg F.C Tablets</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-E1DFA33A95BD</t>
         </is>
       </c>
@@ -1401,7 +1426,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1578,6 +1603,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>APROVASC 300MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-6D020D6B0A4C</t>
         </is>
       </c>
@@ -1601,7 +1631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1772,6 +1802,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-925BB58D4D36</t>
         </is>
       </c>
@@ -1795,7 +1830,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1966,6 +2001,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ADVANTAN 0.1% SKIN OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-0E846E48EA16</t>
         </is>
       </c>
@@ -1989,7 +2029,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2156,6 +2196,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-534A97E4A583</t>
         </is>
       </c>
@@ -2179,7 +2224,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2346,6 +2391,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-29C9279E55C1</t>
         </is>
       </c>
@@ -2369,7 +2419,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2532,6 +2582,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>QATPEN 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-F4A8DC0D47BC</t>
         </is>
       </c>
@@ -2555,7 +2610,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2718,6 +2773,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>RELEZIN 2 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-CC4D4C010A2C</t>
         </is>
       </c>
@@ -2741,7 +2801,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2908,6 +2968,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>MOTILONE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-46370826FADA</t>
         </is>
       </c>
@@ -2931,7 +2996,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3090,6 +3155,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-0BA43C3B00F5</t>
         </is>
       </c>
@@ -3113,7 +3183,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3276,6 +3346,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>RESPAL ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-EC02C1F236AE</t>
         </is>
       </c>
@@ -3299,7 +3374,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3470,6 +3545,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ARCOXIA 120MG TAB</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-E15A80BACAF9</t>
         </is>
       </c>
@@ -3493,7 +3573,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3652,6 +3732,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>QATPEN 150MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-ED27D661A02A</t>
         </is>
       </c>
@@ -3675,7 +3760,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3844,6 +3929,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>DUPHASTON 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-B619C44837C8</t>
         </is>
       </c>
@@ -3867,7 +3957,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4034,6 +4124,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>RELEZIN 4 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-05BC3BF1621C</t>
         </is>
       </c>
@@ -4057,7 +4152,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4216,6 +4311,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>HAIRAL 5% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-2A137FB18AF9</t>
         </is>
       </c>
@@ -4239,7 +4339,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4398,6 +4498,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>QATPEN 200MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-6EC592E0DEB9</t>
         </is>
       </c>
@@ -4421,7 +4526,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4584,6 +4689,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>EDYST 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-3453314C790C</t>
         </is>
       </c>
@@ -4607,7 +4717,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4770,6 +4880,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>MOXIQUIN 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-2AF30879B991</t>
         </is>
       </c>
@@ -4793,7 +4908,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4956,6 +5071,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>ZYROSA 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-0A4313712148</t>
         </is>
       </c>
@@ -4979,7 +5099,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5146,6 +5266,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>RUATINE 20MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-923BFC55563A</t>
         </is>
       </c>
@@ -5169,7 +5294,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5336,6 +5461,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>ZYROSA 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-DC4B0FFEB918</t>
         </is>
       </c>
@@ -5359,7 +5489,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5514,6 +5644,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>MOXIDAD CAPSULES 250MG</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-A752A2D5A910</t>
         </is>
       </c>
@@ -5537,7 +5672,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5698,6 +5833,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>VIVAZAC PLUS 300MG/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-0F087065F8BD</t>
         </is>
       </c>
@@ -5721,7 +5861,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5880,6 +6020,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>GOLD MEDAL MEDICATED OIL</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-A1B06B5009DD</t>
         </is>
       </c>
@@ -5903,7 +6048,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6064,6 +6209,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>VIVAZAC PLUS 300MG/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-B9C3D10120BC</t>
         </is>
       </c>
@@ -6087,7 +6237,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6248,6 +6398,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>VIVAZAC PLUS 150MG/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-504E133E50E7</t>
         </is>
       </c>
@@ -6271,7 +6426,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6438,6 +6593,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>STRATTERA 25MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-DD2E8FD31018</t>
         </is>
       </c>
@@ -6461,7 +6621,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6626,6 +6786,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>VIVAZAC 300MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-B50925A72DAA</t>
         </is>
       </c>
@@ -6649,7 +6814,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6804,6 +6969,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>BRIVIACT 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-89D37312D18B</t>
         </is>
       </c>
@@ -6827,7 +6997,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6994,6 +7164,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>SAFLUTAN 15MCG/ML EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-1FFEA22E724A</t>
         </is>
       </c>
@@ -7017,7 +7192,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7188,6 +7363,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>CARBOSET 600 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-2C549EE8233F</t>
         </is>
       </c>
@@ -7211,7 +7391,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7380,6 +7560,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>DIOZAD</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-B7DF4546BE6F</t>
         </is>
       </c>
@@ -7403,7 +7588,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7574,6 +7759,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>GLEPTAL 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-056C39658181</t>
         </is>
       </c>
@@ -7597,7 +7787,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7758,6 +7948,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>VIVAZAC 150MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-415888430071</t>
         </is>
       </c>
@@ -7781,7 +7976,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7952,6 +8147,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Ravildo 6. 25 mg F.C Tablets</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-955441257F05</t>
         </is>
       </c>
@@ -7975,7 +8175,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8146,6 +8346,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-7BC14E36781C</t>
         </is>
       </c>
@@ -8169,7 +8374,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8344,6 +8549,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ADVANTAN 0.1% SKIN CREAM</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-CE378998B89D</t>
         </is>
       </c>
@@ -8367,7 +8577,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8530,6 +8740,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>AVIALIS 5 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-DA1739F3A2E8</t>
         </is>
       </c>
@@ -8553,7 +8768,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8712,6 +8927,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>AVIALIS 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-0450270D7016</t>
         </is>
       </c>
@@ -8735,7 +8955,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8898,6 +9118,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>AVIALIS 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-F68097E3E76A</t>
         </is>
       </c>
@@ -8921,7 +9146,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9084,6 +9309,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>NAROPIN 10MG-ML AMP</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-E68B29E914FF</t>
         </is>
       </c>
@@ -9107,7 +9337,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9278,6 +9508,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>XIBAX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-2FAD45B4ADB1</t>
         </is>
       </c>
@@ -9301,7 +9536,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9472,6 +9707,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>XIBAX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-8AA4291CBFB7</t>
         </is>
       </c>
@@ -9495,7 +9735,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9662,6 +9902,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>XIBAX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-CDC10021EADB</t>
         </is>
       </c>
@@ -9685,7 +9930,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9852,6 +10097,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>CORTRIEF NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-4AB7CA33E60E</t>
         </is>
       </c>
@@ -9875,7 +10125,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10038,6 +10288,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>MOXIDAD FORTE</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-BE15B73796DE</t>
         </is>
       </c>
@@ -10061,7 +10316,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10232,6 +10487,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ESCIPRA 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-5F428F38362A</t>
         </is>
       </c>
@@ -10255,7 +10515,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10422,6 +10682,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ZALDIAR</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-FB819D2164EC</t>
         </is>
       </c>
@@ -10445,7 +10710,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10608,6 +10873,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ESCIPRA 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-83735696C910</t>
         </is>
       </c>
@@ -10631,7 +10901,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10806,6 +11076,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>STRATTERA 40MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-B28D13C5E19A</t>
         </is>
       </c>
@@ -10829,7 +11104,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10992,6 +11267,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>EVOKA 30 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-79D954ED8FA3</t>
         </is>
       </c>
@@ -11015,7 +11295,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11170,6 +11450,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>BRIVIACT 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-9F25C2E22F39</t>
         </is>
       </c>
@@ -11193,7 +11478,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11364,6 +11649,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Ravildo 12.5 mg F.C Tablets</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-FB50E8E1B745</t>
         </is>
       </c>
@@ -11387,7 +11677,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11562,6 +11852,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>COMBIWAVE</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-B59487104B0B</t>
         </is>
       </c>
@@ -11585,7 +11880,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11740,6 +12035,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>EVOKA 60 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-83D5C9331D95</t>
         </is>
       </c>
@@ -11763,7 +12063,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11938,6 +12238,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>MUCOSOLVAN  30MG-5ML ORAL LIQUID</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-C165ECF792E2</t>
         </is>
       </c>
@@ -11961,7 +12266,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12120,6 +12425,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>XARELTO 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-6A4943D39A73</t>
         </is>
       </c>
@@ -12143,7 +12453,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12306,6 +12616,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>SPASMOLYT 20 MG COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-2933745861FC</t>
         </is>
       </c>
@@ -12329,7 +12644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12500,6 +12815,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>DULCOLAX 5MG ENTERIC COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-A69AA07902DC</t>
         </is>
       </c>
@@ -12523,7 +12843,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12690,6 +13010,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>VOSEVI 400MG/100MG/100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-E8CAA2CC4DFD</t>
         </is>
       </c>
@@ -12713,7 +13038,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12894,6 +13219,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ENBREL 50MG PRE-FILLED PEN</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-94F2D4CA9BD3</t>
         </is>
       </c>
@@ -12917,7 +13247,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13088,6 +13418,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>LOCOID CREAM 0.1%</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-9DF4F791BB1C</t>
         </is>
       </c>
@@ -13111,7 +13446,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13282,6 +13617,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>TRAMAL 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-70D074652A28</t>
         </is>
       </c>
@@ -13305,7 +13645,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13476,6 +13816,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>STRATTERA 60MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-F105A717A639</t>
         </is>
       </c>
@@ -13499,7 +13844,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13662,6 +14007,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>LOCOID LIPO CREAM 0.1%</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-6503D800D5A0</t>
         </is>
       </c>
@@ -13685,7 +14035,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13848,6 +14198,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>BRIVIACT 10MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-50528307657B</t>
         </is>
       </c>
@@ -13871,7 +14226,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14030,6 +14385,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>TRIUM UD Eye Drops</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-481874D258CD</t>
         </is>
       </c>
@@ -14053,7 +14413,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14216,6 +14576,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>LOCOID LOTION 0.1%</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-BF6C2E272AC1</t>
         </is>
       </c>
@@ -14239,7 +14604,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14402,6 +14767,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Ravildo 25 mg F.C Tablets</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-37294FAA476E</t>
         </is>
       </c>
@@ -14425,7 +14795,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14596,6 +14966,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>CLAZ MR 60 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-B330CBE6D851</t>
         </is>
       </c>
@@ -14619,7 +14994,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14782,6 +15157,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>AVORES 400 Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-358E93189DAB</t>
         </is>
       </c>
@@ -14805,7 +15185,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14968,6 +15348,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>AVORES 400 Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-5EB0430E7012</t>
         </is>
       </c>
@@ -14991,7 +15376,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15162,6 +15547,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>TRAMAL 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-6115D6DB3DB6</t>
         </is>
       </c>
@@ -15185,7 +15575,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15352,6 +15742,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>METOJECT 50 mg/ml solution for injection</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-AAF4882F0909</t>
         </is>
       </c>
@@ -15375,7 +15770,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15542,6 +15937,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>ADVIL 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-0635B3C81E3C</t>
         </is>
       </c>
@@ -15565,7 +15965,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15728,6 +16128,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>METOJECT 50 mg/ml solution for injection</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-368F9E5A8A06</t>
         </is>
       </c>
@@ -15751,7 +16156,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15910,6 +16315,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>5%W/V DEXTROSE INJECTION 250ML</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-E0F9F72726AA</t>
         </is>
       </c>
@@ -15933,7 +16343,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16104,6 +16514,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>LAMUCON 500 mg F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-294CDFCF71F1</t>
         </is>
       </c>
@@ -16127,7 +16542,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16286,6 +16701,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>TABIDEX 1 MG F. C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-9F384701603F</t>
         </is>
       </c>
@@ -16309,7 +16729,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16472,6 +16892,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>SEIZET 25 mg Chewable/Dispersible Tablet</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-62716F3EC027</t>
         </is>
       </c>
@@ -16495,7 +16920,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16662,6 +17087,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>VIAGRA 50 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-6B0577BECF21</t>
         </is>
       </c>
@@ -16685,7 +17115,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16836,6 +17266,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Pluryal BOOSTER</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-3A9495E8CD35</t>
         </is>
       </c>
@@ -16859,7 +17294,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17018,6 +17453,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Pluryal VOLUME</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-3A6F7035EE0C</t>
         </is>
       </c>
@@ -17041,7 +17481,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17204,6 +17644,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Pluryal CLASSIC</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-F7A65C787983</t>
         </is>
       </c>
@@ -17227,7 +17672,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17382,6 +17827,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Dolibz</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-0D4D508FB934</t>
         </is>
       </c>
@@ -17405,7 +17855,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17568,6 +18018,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Dolibz</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-56153385D710</t>
         </is>
       </c>
@@ -17591,7 +18046,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17762,6 +18217,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>CIALIS ONCE-A-DAY 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-EB0B1B3075EF</t>
         </is>
       </c>
@@ -17785,7 +18245,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17952,6 +18412,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>GAVISCON ADVANCE PEPPERMINT LIQUID SACHET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-E9EF08854171</t>
         </is>
       </c>
@@ -17975,7 +18440,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18134,6 +18599,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>SILOMES 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-FD1260246AAF</t>
         </is>
       </c>
@@ -18157,7 +18627,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18320,6 +18790,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>GAVISCON ADVANCE PEPPERMINT LIQUID SACHET</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-386AAA8D9B85</t>
         </is>
       </c>
@@ -18343,7 +18818,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18502,6 +18977,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>SILOMES 100 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-36FE8CCF10E2</t>
         </is>
       </c>
@@ -18525,7 +19005,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18700,6 +19180,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>EPANUTIN SUSP 30MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-C91F98CA5ECE</t>
         </is>
       </c>
@@ -18723,7 +19208,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18886,6 +19371,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>FLECTOR EP GRANULES</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-EA6CD6732C64</t>
         </is>
       </c>
@@ -18909,7 +19399,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19080,6 +19570,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>TACROZ FORTE OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-63FA7C24F29A</t>
         </is>
       </c>
@@ -19103,7 +19598,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19262,6 +19757,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>NITYR 2 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-D31AED3516CF</t>
         </is>
       </c>
@@ -19285,7 +19785,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19447,6 +19947,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>DILIZOLEN 600MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-762F0F8E5B81</t>
         </is>
@@ -19463,7 +19968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19509,100 +20014,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19634,7 +20144,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19649,92 +20159,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-16443</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>403.13</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>375</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19766,7 +20281,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19781,92 +20296,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-40450</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>32.69</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>376</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19898,7 +20418,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19913,92 +20433,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-61111</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>219.73</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>377</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20030,7 +20555,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20045,92 +20570,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-84646</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>301.61</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>378</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20162,7 +20692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20177,92 +20707,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-49467</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>348.96</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>379</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20294,7 +20829,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20309,92 +20844,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-70167</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>148.37</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>380</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20426,7 +20966,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20441,92 +20981,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-39072</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>489.3</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>381</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20558,7 +21103,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20573,92 +21118,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-56263</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>139.83</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>382</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20690,7 +21240,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20705,92 +21255,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-63125</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>348.36</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>383</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20822,7 +21377,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20837,92 +21392,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-73540</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>387.69</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>384</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20954,7 +21514,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20969,92 +21529,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-87777</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>440.38</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>385</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21071,7 +21636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21177,6 +21742,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21212,7 +21787,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21277,6 +21852,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-7D363C259ACA</t>
         </is>
@@ -21313,7 +21898,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21378,6 +21963,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-899B25881874</t>
         </is>
@@ -21414,7 +22009,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21479,6 +22074,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-16972F812873</t>
         </is>
@@ -21515,7 +22120,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21580,6 +22185,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-2CDF53A39E89</t>
         </is>
@@ -21616,7 +22231,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21681,6 +22296,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-6215977D941B</t>
         </is>
@@ -21717,7 +22342,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21782,6 +22407,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-1C372B808AB1</t>
         </is>
@@ -21818,7 +22453,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21883,6 +22518,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-F221B0916EB2</t>
         </is>
@@ -21919,7 +22564,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21984,6 +22629,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-B7DCD2F028BC</t>
         </is>
@@ -22020,7 +22675,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22085,6 +22740,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-9F5EA440818A</t>
         </is>
@@ -22121,7 +22786,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22186,6 +22851,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-82C30F97248B</t>
         </is>
@@ -22222,7 +22897,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22287,6 +22962,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-CA2684C76156</t>
         </is>
@@ -22323,7 +23008,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22388,6 +23073,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-C5F8C25AA7D4</t>
         </is>
@@ -22424,7 +23119,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22489,6 +23184,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-FE7DBF423463</t>
         </is>
@@ -22525,7 +23230,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22590,6 +23295,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-1FCB559F181C</t>
         </is>
@@ -22626,7 +23341,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22691,6 +23406,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-56719FA38DD8</t>
         </is>
@@ -22727,7 +23452,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22792,6 +23517,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-7DA694FE0912</t>
         </is>
@@ -22828,7 +23563,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22893,6 +23628,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-80DDD27A943B</t>
         </is>
@@ -22929,7 +23674,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22994,6 +23739,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-0874EFD8E76B</t>
         </is>
@@ -23030,7 +23785,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23095,6 +23850,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-3963C935C114</t>
         </is>
@@ -23131,7 +23896,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23196,6 +23961,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-600A454404FC</t>
         </is>

--- a/product_upload/packages/41/file.xlsx
+++ b/product_upload/packages/41/file.xlsx
@@ -686,8 +686,16 @@
           <t>7408663418-794-255413556488</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CORREX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CORREX 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -873,8 +881,16 @@
           <t>4808732188-562-161081664078</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CAVERTA 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CAVERTA 100MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1060,8 +1076,16 @@
           <t>5821481231-114-923976263103</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIAPHAGE 1 G SR TABLET</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DIAPHAGE 1 G SR TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1247,8 +1271,16 @@
           <t>0641568070-157-217594241189</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ravildo 3.125 mg F.C Tablets</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ravildo 3.125 mg F.C Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -2037,8 +2069,16 @@
           <t>5758205552-512-392849606315</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>GLOFEL 20 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2232,8 +2272,16 @@
           <t>5033990164-449-124750962485</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>QUZAL 400 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2427,8 +2475,16 @@
           <t>6159592074-858-590178636985</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>QATPEN 100MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2809,8 +2865,16 @@
           <t>9818139800-613-695185592557</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOTILONE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MOTILONE 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3004,8 +3068,16 @@
           <t>2548134000-276-617470102979</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>GLOFEL 20 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3191,8 +3263,16 @@
           <t>2558303605-011-808834002458</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESPAL ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>RESPAL ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3581,8 +3661,16 @@
           <t>1174014446-693-258733301257</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN 150MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>QATPEN 150MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -4160,8 +4248,16 @@
           <t>5893659126-234-999776002127</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRAL 5% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>HAIRAL 5% TOPICAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4347,8 +4443,16 @@
           <t>8366723562-833-389732194620</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN 200MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>QATPEN 200MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4534,8 +4638,16 @@
           <t>4536516512-857-711361426648</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EDYST 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>EDYST 20 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4725,8 +4837,16 @@
           <t>8684187641-807-442750191896</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXIQUIN 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>MOXIQUIN 400MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5497,8 +5617,16 @@
           <t>0536875417-963-727576955014</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXIDAD CAPSULES 250MG</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>MOXIDAD CAPSULES 250MG detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5680,8 +5808,16 @@
           <t>8351892007-000-379112358808</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIVAZAC PLUS 300MG/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>VIVAZAC PLUS 300MG/25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -5869,8 +6005,16 @@
           <t>9240709995-683-110490868371</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GOLD MEDAL MEDICATED OIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>GOLD MEDAL MEDICATED OIL detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6056,8 +6200,16 @@
           <t>2892954966-870-324394348160</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIVAZAC PLUS 300MG/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VIVAZAC PLUS 300MG/12.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -6245,8 +6397,16 @@
           <t>0340932119-523-014459239930</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIVAZAC PLUS 150MG/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VIVAZAC PLUS 150MG/12.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -6434,8 +6594,16 @@
           <t>1534954105-395-153194447663</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 25MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>STRATTERA 25MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6629,8 +6797,16 @@
           <t>8772499809-717-217419657196</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIVAZAC 300MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>VIVAZAC 300MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -6822,8 +6998,16 @@
           <t>8263935194-838-585844879324</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>BRIVIACT 25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7399,8 +7583,16 @@
           <t>1266723385-419-487272854598</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOZAD</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DIOZAD detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -7795,8 +7987,16 @@
           <t>9722883747-704-642001911235</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIVAZAC 150MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>VIVAZAC 150MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -8776,8 +8976,16 @@
           <t>7817946868-951-876609329213</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVIALIS 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>AVIALIS 20 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8963,8 +9171,16 @@
           <t>6421370527-419-726893808842</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVIALIS 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>AVIALIS 20 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9154,8 +9370,16 @@
           <t>6204701413-842-099131486214</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NAROPIN 10MG-ML AMP</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>NAROPIN 10MG-ML AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -10133,8 +10357,16 @@
           <t>6739904574-549-391878467573</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXIDAD FORTE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>MOXIDAD FORTE detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10718,8 +10950,16 @@
           <t>5824870691-860-421438810566</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESCIPRA 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ESCIPRA 20MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11112,8 +11352,16 @@
           <t>9699010610-180-108535798310</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVOKA 30 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>EVOKA 30 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11303,8 +11551,16 @@
           <t>3801256677-501-895466078706</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>BRIVIACT 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11888,8 +12144,16 @@
           <t>3751000192-944-726041510569</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVOKA 60 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>EVOKA 60 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12274,8 +12538,16 @@
           <t>3975380292-451-452839310021</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XARELTO 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>XARELTO 2.5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -13653,8 +13925,16 @@
           <t>1711952495-188-140481152118</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 60MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>STRATTERA 60MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -14043,8 +14323,16 @@
           <t>4389962184-879-739185266507</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 10MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>BRIVIACT 10MG/ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14234,8 +14522,16 @@
           <t>8623083001-564-658957399108</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIUM UD Eye Drops</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>TRIUM UD Eye Drops detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14421,8 +14717,16 @@
           <t>8140609532-551-501855594221</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCOID LOTION 0.1%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LOCOID LOTION 0.1% detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -15002,8 +15306,16 @@
           <t>7952911855-869-736166003485</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVORES 400 Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>AVORES 400 Film Coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15193,8 +15505,16 @@
           <t>4547253539-464-050528240349</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVORES 400 Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>AVORES 400 Film Coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -16164,8 +16484,16 @@
           <t>1782712172-278-294213505781</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 5%W/V DEXTROSE INJECTION 250ML</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>5%W/V DEXTROSE INJECTION 250ML detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16550,8 +16878,16 @@
           <t>3495956077-735-037519669860</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TABIDEX 1 MG F. C. TABLET</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TABIDEX 1 MG F. C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16737,8 +17073,16 @@
           <t>6740129960-878-343454261430</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEIZET 25 mg Chewable/Dispersible Tablet</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>SEIZET 25 mg Chewable/Dispersible Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16928,8 +17272,16 @@
           <t>9747618456-425-707135292375</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIAGRA 50 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>VIAGRA 50 mg Orodispersible Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17123,8 +17475,16 @@
           <t>2391555536-104-427859621044</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pluryal BOOSTER</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Pluryal BOOSTER detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17302,8 +17662,16 @@
           <t>9985323927-052-065961978638</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pluryal VOLUME</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Pluryal VOLUME detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17489,8 +17857,16 @@
           <t>5111131644-249-765110724095</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pluryal CLASSIC</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Pluryal CLASSIC detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17680,8 +18056,16 @@
           <t>4455988960-875-473986112339</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dolibz</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Dolibz detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17863,8 +18247,16 @@
           <t>9303560445-335-185507907724</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dolibz</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Dolibz detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18448,8 +18840,16 @@
           <t>6598748140-819-677290484199</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SILOMES 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>SILOMES 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18635,8 +19035,16 @@
           <t>9238625934-899-554261046667</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAVISCON ADVANCE PEPPERMINT LIQUID SACHET</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>GAVISCON ADVANCE PEPPERMINT LIQUID SACHET detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18826,8 +19234,16 @@
           <t>5170011835-047-880740210916</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SILOMES 100 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>SILOMES 100 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19216,8 +19632,16 @@
           <t>3107497969-140-153531738139</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLECTOR EP GRANULES</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>FLECTOR EP GRANULES detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19606,8 +20030,16 @@
           <t>1708456649-133-234514766184</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NITYR 2 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>NITYR 2 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19793,8 +20225,16 @@
           <t>1267209331-712-372155870742</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DILIZOLEN 600MG TABLET</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>DILIZOLEN 600MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/41/file.xlsx
+++ b/product_upload/packages/41/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22076,7 +22076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22157,40 +22157,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22270,38 +22275,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>173.34</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-7D363C259ACA</t>
         </is>
@@ -22381,38 +22391,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>213.87</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-899B25881874</t>
         </is>
@@ -22492,38 +22507,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>84.56</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-16972F812873</t>
         </is>
@@ -22603,38 +22623,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>435.14</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-2CDF53A39E89</t>
         </is>
@@ -22714,38 +22739,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>90.70999999999999</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-6215977D941B</t>
         </is>
@@ -22825,38 +22855,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>492.54</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-1C372B808AB1</t>
         </is>
@@ -22936,38 +22971,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>463.84</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-F221B0916EB2</t>
         </is>
@@ -23047,38 +23087,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>463.28</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-B7DCD2F028BC</t>
         </is>
@@ -23158,38 +23203,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>185.18</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-9F5EA440818A</t>
         </is>
@@ -23269,38 +23319,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>140.58</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-82C30F97248B</t>
         </is>
@@ -23380,38 +23435,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>86.68000000000001</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-CA2684C76156</t>
         </is>
@@ -23491,38 +23551,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>87.88</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-C5F8C25AA7D4</t>
         </is>
@@ -23602,38 +23667,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>230.04</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-FE7DBF423463</t>
         </is>
@@ -23713,38 +23783,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>319.99</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-1FCB559F181C</t>
         </is>
@@ -23824,38 +23899,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>104.47</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-56719FA38DD8</t>
         </is>
@@ -23935,38 +24015,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>438.49</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-7DA694FE0912</t>
         </is>
@@ -24046,38 +24131,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>499.7</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-80DDD27A943B</t>
         </is>
@@ -24157,38 +24247,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>388.27</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-0874EFD8E76B</t>
         </is>
@@ -24268,38 +24363,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>374.89</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-3963C935C114</t>
         </is>
@@ -24379,38 +24479,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>137.39</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-600A454404FC</t>
         </is>
